--- a/Data/Output/Contract Sent Summary Report.xlsx
+++ b/Data/Output/Contract Sent Summary Report.xlsx
@@ -40,7 +40,7 @@
     <x:t>Status</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_204643</x:t>
+    <x:t>20260317_192128</x:t>
   </x:si>
   <x:si>
     <x:t>Crisp Accountancy Ltd</x:t>
@@ -52,7 +52,7 @@
     <x:t>Flagged Mandatory Info Missed</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_205022</x:t>
+    <x:t>20260317_192334</x:t>
   </x:si>
   <x:si>
     <x:t>Parkworth</x:t>
@@ -61,7 +61,7 @@
     <x:t>Parkworth - PT Paraplanner</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_205149</x:t>
+    <x:t>20260317_192550</x:t>
   </x:si>
   <x:si>
     <x:t>Aspire Retire Financial Services</x:t>
@@ -70,7 +70,7 @@
     <x:t>Aspire Retire Financial Services - Process Enhancement</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_205327</x:t>
+    <x:t>20260317_192827</x:t>
   </x:si>
   <x:si>
     <x:t>Tworek Investment Pty Ltd ATF Insight Wealth Unit Trust T/A Insight Wealth Planning</x:t>
@@ -79,13 +79,13 @@
     <x:t>Insight Wealth - PT Paraplanner 6</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_205556</x:t>
+    <x:t>20260317_193012</x:t>
   </x:si>
   <x:si>
     <x:t>Insight Wealth - PT Paraplanner 7</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_205729</x:t>
+    <x:t>20260317_193149</x:t>
   </x:si>
   <x:si>
     <x:t>Kerfab</x:t>
@@ -94,7 +94,7 @@
     <x:t>Kerfab - NetSuite MCP Integration &amp; ROI Qualification Sprint</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_205901</x:t>
+    <x:t>20260317_193401</x:t>
   </x:si>
   <x:si>
     <x:t>Bridgewater</x:t>
@@ -103,13 +103,16 @@
     <x:t>Bridgewater Construction - Subcont Payment Management DA Imp</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_210028</x:t>
+    <x:t>20260317_193602</x:t>
   </x:si>
   <x:si>
     <x:t>Bridgewater Construction - Subcontractor Payment Process DA Imp</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_210240</x:t>
+    <x:t>Completed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260317_193800</x:t>
   </x:si>
   <x:si>
     <x:t>MWA Financial Ltd</x:t>
@@ -118,13 +121,13 @@
     <x:t>MWA - Anuj &amp; Trisha (Feb - 70 Hors)</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_210500</x:t>
+    <x:t>20260317_194009</x:t>
   </x:si>
   <x:si>
     <x:t>Bridgewater - Recurring</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_210815</x:t>
+    <x:t>20260317_194218</x:t>
   </x:si>
   <x:si>
     <x:t>Newmarket Business Services Ltd</x:t>
@@ -133,7 +136,7 @@
     <x:t>SBA (NM) - FT Accountant (2)</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_211025</x:t>
+    <x:t>20260317_194420</x:t>
   </x:si>
   <x:si>
     <x:t>Wren Sterling Financial Planning Limited</x:t>
@@ -142,13 +145,22 @@
     <x:t>Wren Sterling_DA Implementation_ATR_Sent_to_Client</x:t>
   </x:si>
   <x:si>
-    <x:t>20260310_211125</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evolve Accounting Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Evolve Accounting Ltd - FT Accountant</x:t>
+    <x:t>20260317_194618</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hood Sweeney</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hood Sweeney - Data Analytics Survey Process</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260317_194934</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gallagher Benefit Services Pty Ltd (Brisbane)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gallagher - Data Migration (2 Week FT)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -609,18 +621,18 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>7</x:v>
@@ -628,13 +640,13 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>7</x:v>
@@ -642,13 +654,13 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>7</x:v>
@@ -656,13 +668,13 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>7</x:v>
@@ -670,15 +682,29 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:4">
+      <x:c r="A15" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>

--- a/Data/Output/Contract Sent Summary Report.xlsx
+++ b/Data/Output/Contract Sent Summary Report.xlsx
@@ -40,7 +40,7 @@
     <x:t>Status</x:t>
   </x:si>
   <x:si>
-    <x:t>20260317_192128</x:t>
+    <x:t>20260319_055551</x:t>
   </x:si>
   <x:si>
     <x:t>Crisp Accountancy Ltd</x:t>
@@ -49,118 +49,7 @@
     <x:t>Crisp - PT Accountant</x:t>
   </x:si>
   <x:si>
-    <x:t>Flagged Mandatory Info Missed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_192334</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Parkworth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Parkworth - PT Paraplanner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_192550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aspire Retire Financial Services</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aspire Retire Financial Services - Process Enhancement</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_192827</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tworek Investment Pty Ltd ATF Insight Wealth Unit Trust T/A Insight Wealth Planning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Insight Wealth - PT Paraplanner 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_193012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Insight Wealth - PT Paraplanner 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_193149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kerfab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kerfab - NetSuite MCP Integration &amp; ROI Qualification Sprint</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_193401</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bridgewater</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bridgewater Construction - Subcont Payment Management DA Imp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_193602</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bridgewater Construction - Subcontractor Payment Process DA Imp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Completed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_193800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MWA Financial Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MWA - Anuj &amp; Trisha (Feb - 70 Hors)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_194009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bridgewater - Recurring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_194218</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Newmarket Business Services Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SBA (NM) - FT Accountant (2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_194420</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wren Sterling Financial Planning Limited</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wren Sterling_DA Implementation_ATR_Sent_to_Client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_194618</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hood Sweeney</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hood Sweeney - Data Analytics Survey Process</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20260317_194934</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gallagher Benefit Services Pty Ltd (Brisbane)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gallagher - Data Migration (2 Week FT)</x:t>
+    <x:t>Flagged Email Mismatch</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -526,188 +415,6 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:4">
-      <x:c r="A7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:4">
-      <x:c r="A8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:4">
-      <x:c r="A9" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:4">
-      <x:c r="A10" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:4">
-      <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:4">
-      <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:4">
-      <x:c r="A13" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:4">
-      <x:c r="A14" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:4">
-      <x:c r="A15" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Output/Contract Sent Summary Report.xlsx
+++ b/Data/Output/Contract Sent Summary Report.xlsx
@@ -40,7 +40,7 @@
     <x:t>Status</x:t>
   </x:si>
   <x:si>
-    <x:t>20260319_055551</x:t>
+    <x:t>20260325_191413</x:t>
   </x:si>
   <x:si>
     <x:t>Crisp Accountancy Ltd</x:t>
@@ -50,6 +50,99 @@
   </x:si>
   <x:si>
     <x:t>Flagged Email Mismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_192126</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aspire Retire Financial Services</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aspire Retire Financial Services - Process Enhancement</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_192304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kerfab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kerfab - NetSuite MCP Integration &amp; ROI Qualification Sprint</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Flagged Mandatory Info Missed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_192502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bridgewater</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bridgewater Construction - Subcont Payment Management DA Imp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_192709</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bridgewater - Recurring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_193201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hood Sweeney</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hood Sweeney - Data Analytics Survey Process</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_193406</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Smith &amp; Co Financial Services Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Smith &amp; Co - 2hr/day PP (2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_193508</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ashfords Accountants &amp; Advisory Pty Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ashfords - DA Implementation - Compliance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_193856</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kelly Partners Group Holdings Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kelly Partners BAS - DA Implementation - GovReports Update</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_194025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Payroll Sorted Limited</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Payroll Sorted - Additional BOT 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20260325_194218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3P Corporation Limited</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3P Corporation Limited_HubSpot Implementation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Flagged Lack of Information</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -415,6 +508,146 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" spans="1:4">
+      <x:c r="A3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:4">
+      <x:c r="A4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:4">
+      <x:c r="A5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:4">
+      <x:c r="A8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:4">
+      <x:c r="A9" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:4">
+      <x:c r="A11" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:4">
+      <x:c r="A12" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
